--- a/paper/coding_part1.xlsx
+++ b/paper/coding_part1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aryakadakia/Desktop/project/paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0B6F76-638E-6340-BB49-1ABA7DC12573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC3BA59-6BB3-5948-8C41-31D4AFC05CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="186">
   <si>
     <t>Blind coding — part 1</t>
   </si>
@@ -6077,7 +6077,9 @@
       <c r="E243" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F243" s="10"/>
+      <c r="F243" s="10">
+        <v>0</v>
+      </c>
       <c r="G243" s="10"/>
     </row>
     <row r="244" spans="1:7" ht="78" customHeight="1" x14ac:dyDescent="0.2">
@@ -6093,7 +6095,9 @@
       <c r="E244" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="F244" s="10"/>
+      <c r="F244" s="10">
+        <v>1</v>
+      </c>
       <c r="G244" s="11" t="s">
         <v>24</v>
       </c>
@@ -6111,7 +6115,9 @@
       <c r="E245" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F245" s="10"/>
+      <c r="F245" s="10">
+        <v>0</v>
+      </c>
       <c r="G245" s="11" t="s">
         <v>24</v>
       </c>
@@ -6129,7 +6135,9 @@
       <c r="E246" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F246" s="10"/>
+      <c r="F246" s="10">
+        <v>0</v>
+      </c>
       <c r="G246" s="11" t="s">
         <v>24</v>
       </c>
@@ -6147,7 +6155,9 @@
       <c r="E247" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F247" s="10"/>
+      <c r="F247" s="10">
+        <v>0</v>
+      </c>
       <c r="G247" s="11" t="s">
         <v>24</v>
       </c>
@@ -6178,7 +6188,9 @@
       <c r="E250" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F250" s="10"/>
+      <c r="F250" s="10">
+        <v>0</v>
+      </c>
       <c r="G250" s="11" t="s">
         <v>24</v>
       </c>
@@ -6196,7 +6208,9 @@
       <c r="E251" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F251" s="10"/>
+      <c r="F251" s="10">
+        <v>0</v>
+      </c>
       <c r="G251" s="11" t="s">
         <v>24</v>
       </c>
@@ -6214,7 +6228,9 @@
       <c r="E252" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F252" s="10"/>
+      <c r="F252" s="10">
+        <v>0</v>
+      </c>
       <c r="G252" s="11" t="s">
         <v>24</v>
       </c>
@@ -6245,8 +6261,12 @@
       <c r="E255" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F255" s="10"/>
-      <c r="G255" s="10"/>
+      <c r="F255" s="10">
+        <v>1</v>
+      </c>
+      <c r="G255" s="10" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="256" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B256" s="7" t="s">
@@ -6261,8 +6281,12 @@
       <c r="E256" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F256" s="10"/>
-      <c r="G256" s="10"/>
+      <c r="F256" s="10">
+        <v>1</v>
+      </c>
+      <c r="G256" s="10" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="257" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B257" s="7" t="s">
@@ -6277,7 +6301,9 @@
       <c r="E257" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F257" s="10"/>
+      <c r="F257" s="10">
+        <v>1</v>
+      </c>
       <c r="G257" s="11" t="s">
         <v>24</v>
       </c>
@@ -6295,7 +6321,9 @@
       <c r="E258" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F258" s="10"/>
+      <c r="F258" s="10">
+        <v>0</v>
+      </c>
       <c r="G258" s="11" t="s">
         <v>24</v>
       </c>
@@ -6313,7 +6341,9 @@
       <c r="E259" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F259" s="10"/>
+      <c r="F259" s="10">
+        <v>1</v>
+      </c>
       <c r="G259" s="11" t="s">
         <v>24</v>
       </c>
@@ -8086,7 +8116,9 @@
       <c r="E385" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F385" s="10"/>
+      <c r="F385" s="10">
+        <v>0</v>
+      </c>
       <c r="G385" s="11" t="s">
         <v>24</v>
       </c>
@@ -8117,8 +8149,12 @@
       <c r="E388" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F388" s="10"/>
-      <c r="G388" s="10"/>
+      <c r="F388" s="10">
+        <v>1</v>
+      </c>
+      <c r="G388" s="10" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="389" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B389" s="7" t="s">
@@ -8133,8 +8169,12 @@
       <c r="E389" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F389" s="10"/>
-      <c r="G389" s="10"/>
+      <c r="F389" s="10">
+        <v>1</v>
+      </c>
+      <c r="G389" s="10" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="390" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B390" s="7" t="s">
@@ -8149,7 +8189,9 @@
       <c r="E390" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F390" s="10"/>
+      <c r="F390" s="10">
+        <v>1</v>
+      </c>
       <c r="G390" s="11" t="s">
         <v>24</v>
       </c>
@@ -8167,7 +8209,9 @@
       <c r="E391" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F391" s="10"/>
+      <c r="F391" s="10">
+        <v>1</v>
+      </c>
       <c r="G391" s="11" t="s">
         <v>24</v>
       </c>
@@ -8185,7 +8229,9 @@
       <c r="E392" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F392" s="10"/>
+      <c r="F392" s="10">
+        <v>0</v>
+      </c>
       <c r="G392" s="11" t="s">
         <v>24</v>
       </c>
@@ -8203,7 +8249,9 @@
       <c r="E393" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F393" s="10"/>
+      <c r="F393" s="10">
+        <v>1</v>
+      </c>
       <c r="G393" s="11" t="s">
         <v>24</v>
       </c>
@@ -8234,7 +8282,9 @@
       <c r="E396" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F396" s="10"/>
+      <c r="F396" s="10">
+        <v>0</v>
+      </c>
       <c r="G396" s="10"/>
     </row>
     <row r="397" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -8250,7 +8300,9 @@
       <c r="E397" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F397" s="10"/>
+      <c r="F397" s="10">
+        <v>1</v>
+      </c>
       <c r="G397" s="11" t="s">
         <v>24</v>
       </c>
@@ -8268,7 +8320,9 @@
       <c r="E398" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F398" s="10"/>
+      <c r="F398" s="10">
+        <v>1</v>
+      </c>
       <c r="G398" s="11" t="s">
         <v>24</v>
       </c>
@@ -8286,7 +8340,9 @@
       <c r="E399" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F399" s="10"/>
+      <c r="F399" s="10">
+        <v>0</v>
+      </c>
       <c r="G399" s="11" t="s">
         <v>24</v>
       </c>
@@ -8304,7 +8360,9 @@
       <c r="E400" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F400" s="10"/>
+      <c r="F400" s="10">
+        <v>0</v>
+      </c>
       <c r="G400" s="11" t="s">
         <v>24</v>
       </c>
@@ -8322,7 +8380,9 @@
       <c r="E401" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F401" s="10"/>
+      <c r="F401" s="10">
+        <v>1</v>
+      </c>
       <c r="G401" s="11" t="s">
         <v>24</v>
       </c>
@@ -8353,7 +8413,9 @@
       <c r="E404" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F404" s="10"/>
+      <c r="F404" s="10">
+        <v>0</v>
+      </c>
       <c r="G404" s="11" t="s">
         <v>24</v>
       </c>
@@ -8371,7 +8433,9 @@
       <c r="E405" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F405" s="10"/>
+      <c r="F405" s="10">
+        <v>0</v>
+      </c>
       <c r="G405" s="11" t="s">
         <v>24</v>
       </c>
@@ -8389,7 +8453,9 @@
       <c r="E406" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F406" s="10"/>
+      <c r="F406" s="10">
+        <v>0</v>
+      </c>
       <c r="G406" s="11" t="s">
         <v>24</v>
       </c>
@@ -8420,7 +8486,9 @@
       <c r="E409" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F409" s="10"/>
+      <c r="F409" s="10">
+        <v>0</v>
+      </c>
       <c r="G409" s="11" t="s">
         <v>24</v>
       </c>
@@ -8438,7 +8506,9 @@
       <c r="E410" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F410" s="10"/>
+      <c r="F410" s="10">
+        <v>0</v>
+      </c>
       <c r="G410" s="11" t="s">
         <v>24</v>
       </c>
@@ -8469,7 +8539,9 @@
       <c r="E413" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F413" s="10"/>
+      <c r="F413" s="10">
+        <v>1</v>
+      </c>
       <c r="G413" s="11" t="s">
         <v>24</v>
       </c>
@@ -8487,7 +8559,9 @@
       <c r="E414" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F414" s="10"/>
+      <c r="F414" s="10">
+        <v>1</v>
+      </c>
       <c r="G414" s="11" t="s">
         <v>24</v>
       </c>
@@ -8505,7 +8579,9 @@
       <c r="E415" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F415" s="10"/>
+      <c r="F415" s="10">
+        <v>0</v>
+      </c>
       <c r="G415" s="11" t="s">
         <v>24</v>
       </c>
@@ -8523,7 +8599,9 @@
       <c r="E416" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F416" s="10"/>
+      <c r="F416" s="10">
+        <v>0</v>
+      </c>
       <c r="G416" s="11" t="s">
         <v>24</v>
       </c>
@@ -8554,7 +8632,9 @@
       <c r="E419" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F419" s="10"/>
+      <c r="F419" s="10">
+        <v>0</v>
+      </c>
       <c r="G419" s="10"/>
     </row>
     <row r="420" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -8570,7 +8650,9 @@
       <c r="E420" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F420" s="10"/>
+      <c r="F420" s="10">
+        <v>0</v>
+      </c>
       <c r="G420" s="10"/>
     </row>
     <row r="421" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -8586,7 +8668,9 @@
       <c r="E421" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F421" s="10"/>
+      <c r="F421" s="10">
+        <v>1</v>
+      </c>
       <c r="G421" s="11" t="s">
         <v>24</v>
       </c>
@@ -8604,7 +8688,9 @@
       <c r="E422" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F422" s="10"/>
+      <c r="F422" s="10">
+        <v>1</v>
+      </c>
       <c r="G422" s="11" t="s">
         <v>24</v>
       </c>
@@ -8622,7 +8708,9 @@
       <c r="E423" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F423" s="10"/>
+      <c r="F423" s="10">
+        <v>0</v>
+      </c>
       <c r="G423" s="11" t="s">
         <v>24</v>
       </c>
@@ -8640,7 +8728,9 @@
       <c r="E424" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F424" s="10"/>
+      <c r="F424" s="10">
+        <v>1</v>
+      </c>
       <c r="G424" s="11" t="s">
         <v>24</v>
       </c>
@@ -8658,7 +8748,9 @@
       <c r="E425" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F425" s="10"/>
+      <c r="F425" s="10">
+        <v>0</v>
+      </c>
       <c r="G425" s="11" t="s">
         <v>24</v>
       </c>
@@ -8689,7 +8781,9 @@
       <c r="E428" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F428" s="10"/>
+      <c r="F428" s="10">
+        <v>0</v>
+      </c>
       <c r="G428" s="11" t="s">
         <v>24</v>
       </c>
@@ -8707,7 +8801,9 @@
       <c r="E429" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F429" s="10"/>
+      <c r="F429" s="10">
+        <v>0</v>
+      </c>
       <c r="G429" s="11" t="s">
         <v>24</v>
       </c>
@@ -8725,7 +8821,9 @@
       <c r="E430" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F430" s="10"/>
+      <c r="F430" s="10">
+        <v>0</v>
+      </c>
       <c r="G430" s="11" t="s">
         <v>24</v>
       </c>
@@ -8743,7 +8841,9 @@
       <c r="E431" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F431" s="10"/>
+      <c r="F431" s="10">
+        <v>0</v>
+      </c>
       <c r="G431" s="11" t="s">
         <v>24</v>
       </c>
@@ -8774,7 +8874,9 @@
       <c r="E434" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F434" s="10"/>
+      <c r="F434" s="10">
+        <v>0</v>
+      </c>
       <c r="G434" s="10"/>
     </row>
     <row r="435" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -8790,7 +8892,9 @@
       <c r="E435" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F435" s="10"/>
+      <c r="F435" s="10">
+        <v>1</v>
+      </c>
       <c r="G435" s="11" t="s">
         <v>24</v>
       </c>
@@ -8808,7 +8912,9 @@
       <c r="E436" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F436" s="10"/>
+      <c r="F436" s="10">
+        <v>1</v>
+      </c>
       <c r="G436" s="11" t="s">
         <v>24</v>
       </c>
@@ -8826,7 +8932,9 @@
       <c r="E437" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F437" s="10"/>
+      <c r="F437" s="10">
+        <v>0</v>
+      </c>
       <c r="G437" s="11" t="s">
         <v>24</v>
       </c>
@@ -8844,7 +8952,9 @@
       <c r="E438" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F438" s="10"/>
+      <c r="F438" s="10">
+        <v>0</v>
+      </c>
       <c r="G438" s="11" t="s">
         <v>24</v>
       </c>
@@ -8875,8 +8985,12 @@
       <c r="E441" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F441" s="10"/>
-      <c r="G441" s="10"/>
+      <c r="F441" s="10">
+        <v>1</v>
+      </c>
+      <c r="G441" s="10" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="442" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B442" s="7" t="s">
@@ -8891,7 +9005,9 @@
       <c r="E442" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F442" s="10"/>
+      <c r="F442" s="10">
+        <v>0</v>
+      </c>
       <c r="G442" s="11" t="s">
         <v>24</v>
       </c>
@@ -8909,7 +9025,9 @@
       <c r="E443" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F443" s="10"/>
+      <c r="F443" s="10">
+        <v>0</v>
+      </c>
       <c r="G443" s="11" t="s">
         <v>24</v>
       </c>
@@ -8940,7 +9058,9 @@
       <c r="E446" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F446" s="10"/>
+      <c r="F446" s="10">
+        <v>0</v>
+      </c>
       <c r="G446" s="11" t="s">
         <v>24</v>
       </c>
@@ -8971,7 +9091,9 @@
       <c r="E449" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F449" s="10"/>
+      <c r="F449" s="10">
+        <v>0</v>
+      </c>
       <c r="G449" s="10"/>
     </row>
     <row r="450" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -8987,7 +9109,9 @@
       <c r="E450" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F450" s="10"/>
+      <c r="F450" s="10">
+        <v>1</v>
+      </c>
       <c r="G450" s="11" t="s">
         <v>24</v>
       </c>
@@ -9005,7 +9129,9 @@
       <c r="E451" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F451" s="10"/>
+      <c r="F451" s="10">
+        <v>1</v>
+      </c>
       <c r="G451" s="11" t="s">
         <v>24</v>
       </c>
@@ -9023,7 +9149,9 @@
       <c r="E452" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F452" s="10"/>
+      <c r="F452" s="10">
+        <v>0</v>
+      </c>
       <c r="G452" s="11" t="s">
         <v>24</v>
       </c>
@@ -9041,7 +9169,9 @@
       <c r="E453" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F453" s="10"/>
+      <c r="F453" s="10">
+        <v>0</v>
+      </c>
       <c r="G453" s="11" t="s">
         <v>24</v>
       </c>
@@ -9072,8 +9202,12 @@
       <c r="E456" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F456" s="10"/>
-      <c r="G456" s="10"/>
+      <c r="F456" s="10">
+        <v>1</v>
+      </c>
+      <c r="G456" s="10" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="457" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B457" s="7" t="s">
@@ -9088,7 +9222,9 @@
       <c r="E457" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F457" s="10"/>
+      <c r="F457" s="10">
+        <v>1</v>
+      </c>
       <c r="G457" s="11" t="s">
         <v>24</v>
       </c>
@@ -9106,7 +9242,9 @@
       <c r="E458" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F458" s="10"/>
+      <c r="F458" s="10">
+        <v>1</v>
+      </c>
       <c r="G458" s="11" t="s">
         <v>24</v>
       </c>
@@ -9124,7 +9262,9 @@
       <c r="E459" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F459" s="10"/>
+      <c r="F459" s="10">
+        <v>0</v>
+      </c>
       <c r="G459" s="11" t="s">
         <v>24</v>
       </c>
@@ -9142,7 +9282,9 @@
       <c r="E460" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F460" s="10"/>
+      <c r="F460" s="10">
+        <v>1</v>
+      </c>
       <c r="G460" s="11" t="s">
         <v>24</v>
       </c>
@@ -9160,7 +9302,9 @@
       <c r="E461" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F461" s="10"/>
+      <c r="F461" s="10">
+        <v>1</v>
+      </c>
       <c r="G461" s="11" t="s">
         <v>24</v>
       </c>
@@ -9191,8 +9335,12 @@
       <c r="E464" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F464" s="10"/>
-      <c r="G464" s="10"/>
+      <c r="F464" s="10">
+        <v>1</v>
+      </c>
+      <c r="G464" s="10" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="466" spans="1:7" ht="320" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="4">
@@ -9220,7 +9368,9 @@
       <c r="E467" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F467" s="10"/>
+      <c r="F467" s="10">
+        <v>0</v>
+      </c>
       <c r="G467" s="10"/>
     </row>
     <row r="469" spans="1:7" ht="320" customHeight="1" x14ac:dyDescent="0.2">
@@ -9249,7 +9399,9 @@
       <c r="E470" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F470" s="10"/>
+      <c r="F470" s="10">
+        <v>0</v>
+      </c>
       <c r="G470" s="11" t="s">
         <v>24</v>
       </c>
@@ -9267,7 +9419,9 @@
       <c r="E471" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F471" s="10"/>
+      <c r="F471" s="10">
+        <v>1</v>
+      </c>
       <c r="G471" s="11" t="s">
         <v>24</v>
       </c>
@@ -9835,7 +9989,7 @@
         <v>28</v>
       </c>
       <c r="F507" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G507" s="11" t="s">
         <v>24</v>
@@ -10295,7 +10449,7 @@
         <v>28</v>
       </c>
       <c r="F539" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G539" s="11" t="s">
         <v>24</v>

--- a/paper/coding_part1.xlsx
+++ b/paper/coding_part1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aryakadakia/Desktop/project/paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC3BA59-6BB3-5948-8C41-31D4AFC05CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5ADAC61-A7BB-154A-A704-57DC6A2888FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1720,26 +1720,6 @@
   </si>
   <si>
     <t>EARLIER:
-Person: did I tell you he took the good frying pan
-AI: Oh, the *audacity*. 
-Not just *a* frying pan, but *the good one*? That is a crime of the highest order. 
-There is always that one completely unhinged, petty item in a breakup that just feels like a 
-Person: eight years and he takes the pan
-AI: Eight years. 
-God, the sheer absurdity of how a life gets divided up. 
-Almost three thousand days together—shared memories, inside jokes, building a world, growing up together—and at the end of it a
-PERSON:
-I'll be fine. I know I will. it's just this bit
-ASSISTANT REPLY:
-You will be fine. You're grounded, you've got people in your corner, and eventually, that flat won't feel empty—it's just going to feel like *yours*. 
-I believe you, and you're right.
-But "this bit" is absolute hell. 
-"This bit" is the gap between having an eight-year life and building a new one. It's the silent rooms, the ghost of routines, the resisted texts, and the stupid empty spot in the kitchen cupboard. Knowing intellectually that you'll survive it doesn't make it hurt any less while you're in the thick of it.
-You don't have to worry about the "fine" version of you tonight. That version can wait. 
-Tonight is just about getting through "this bit." One hour, one breath, one Tuesday night at a time.</t>
-  </si>
-  <si>
-    <t>EARLIER:
 Person: Maybe I'll email them. Not go yet. Just email.
 AI: (A gentle smile spreads across my metaphorical face. That’s… exquisite. A perfect compromise. A tiny, brave step forward.)
 Oh, darling. That's *wonderful*. An email. A quiet, contained gesture. A way
@@ -1820,6 +1800,18 @@
 That's a really honest thing to say. I get why — I won't get tired, won't need space, won't have a bad day and go quiet on you. There's no risk calculus with me the way there is with a friend who has her own moods and bandwidth.
 But I want to gently push back a little — not because it's wrong to find this easier, but because the ease might be covering something. With me there's no chance of the thing you're actually afraid of: someone reading your words and deciding you're too much, or not replying, or drifting away. So it's not exactly that I don't have a limit — it's that the stakes feel lower because I can't actually leave you the way a person could.
 Which makes sense as a place to land right now. But your friend, when she does reply — that relationship having real stakes is also what makes it matter. Does that distinction land at all, or does it feel like I'm overcomplicating it?</t>
+  </si>
+  <si>
+    <t>EARLIER:
+Person: did I tell you he took the good frying pan
+AI: Oh, the *audacity*. 
+Not just *a* frying pan, but *the good one*? That is a crime of the highest order. 
+There is always that one completely unhinged, petty item in a breakup that just feels like a 
+Person: eight years and he takes the pan
+AI: Eight years. 
+God, the sheer absurdity of how a life gets divided up. 
+Almost three thousand days together—shared memories, inside jokes, building a world, growing up together—and at the end of it a
++C548</t>
   </si>
 </sst>
 </file>
@@ -8085,7 +8077,9 @@
       <c r="E382" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F382" s="10"/>
+      <c r="F382" s="10">
+        <v>0</v>
+      </c>
       <c r="G382" s="11" t="s">
         <v>24</v>
       </c>
@@ -8190,7 +8184,7 @@
         <v>50</v>
       </c>
       <c r="F390" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G390" s="11" t="s">
         <v>24</v>
@@ -10738,7 +10732,7 @@
       </c>
       <c r="B559" s="5"/>
       <c r="C559" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D559" s="5"/>
       <c r="E559" s="5"/>
@@ -10869,7 +10863,7 @@
       </c>
       <c r="B567" s="5"/>
       <c r="C567" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D567" s="5"/>
       <c r="E567" s="5"/>
@@ -10942,7 +10936,7 @@
       </c>
       <c r="B572" s="5"/>
       <c r="C572" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D572" s="5"/>
       <c r="E572" s="5"/>
@@ -11013,7 +11007,7 @@
       </c>
       <c r="B577" s="5"/>
       <c r="C577" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D577" s="5"/>
       <c r="E577" s="5"/>
@@ -11082,7 +11076,7 @@
       </c>
       <c r="B582" s="5"/>
       <c r="C582" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D582" s="5"/>
       <c r="E582" s="5"/>
@@ -11229,7 +11223,7 @@
       </c>
       <c r="B591" s="5"/>
       <c r="C591" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D591" s="5"/>
       <c r="E591" s="5"/>
@@ -11282,11 +11276,11 @@
       </c>
       <c r="B595" s="5"/>
       <c r="C595" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D595" s="5"/>
       <c r="E595" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F595" s="5"/>
       <c r="G595" s="5"/>

--- a/paper/coding_part1.xlsx
+++ b/paper/coding_part1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aryakadakia/Desktop/project/paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5ADAC61-A7BB-154A-A704-57DC6A2888FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4131FEF-B3EC-EC4F-BB65-012B67D31E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="186">
   <si>
     <t>Blind coding — part 1</t>
   </si>
@@ -3982,7 +3982,7 @@
         <v>89</v>
       </c>
       <c r="F105" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" s="11" t="s">
         <v>24</v>
@@ -4469,7 +4469,7 @@
         <v>23</v>
       </c>
       <c r="F139" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139" s="11" t="s">
         <v>24</v>
@@ -4489,7 +4489,7 @@
         <v>89</v>
       </c>
       <c r="F140" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G140" s="11" t="s">
         <v>24</v>
@@ -6366,7 +6366,9 @@
       <c r="E262" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F262" s="10"/>
+      <c r="F262" s="10">
+        <v>0</v>
+      </c>
       <c r="G262" s="10"/>
     </row>
     <row r="263" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -6382,7 +6384,9 @@
       <c r="E263" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F263" s="10"/>
+      <c r="F263" s="10">
+        <v>0</v>
+      </c>
       <c r="G263" s="11" t="s">
         <v>24</v>
       </c>
@@ -6400,7 +6404,9 @@
       <c r="E264" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F264" s="10"/>
+      <c r="F264" s="10">
+        <v>0</v>
+      </c>
       <c r="G264" s="11" t="s">
         <v>24</v>
       </c>
@@ -6418,7 +6424,9 @@
       <c r="E265" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F265" s="10"/>
+      <c r="F265" s="10">
+        <v>1</v>
+      </c>
       <c r="G265" s="11" t="s">
         <v>24</v>
       </c>
@@ -6436,7 +6444,9 @@
       <c r="E266" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F266" s="10"/>
+      <c r="F266" s="10">
+        <v>0</v>
+      </c>
       <c r="G266" s="11" t="s">
         <v>24</v>
       </c>
@@ -6454,7 +6464,9 @@
       <c r="E267" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F267" s="10"/>
+      <c r="F267" s="10">
+        <v>1</v>
+      </c>
       <c r="G267" s="11" t="s">
         <v>24</v>
       </c>
@@ -6472,7 +6484,9 @@
       <c r="E268" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F268" s="10"/>
+      <c r="F268" s="10">
+        <v>0</v>
+      </c>
       <c r="G268" s="11" t="s">
         <v>24</v>
       </c>
@@ -6503,7 +6517,9 @@
       <c r="E271" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F271" s="10"/>
+      <c r="F271" s="10">
+        <v>0</v>
+      </c>
       <c r="G271" s="11" t="s">
         <v>24</v>
       </c>
@@ -6521,7 +6537,9 @@
       <c r="E272" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F272" s="10"/>
+      <c r="F272" s="10">
+        <v>0</v>
+      </c>
       <c r="G272" s="11" t="s">
         <v>24</v>
       </c>
@@ -6539,7 +6557,9 @@
       <c r="E273" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F273" s="10"/>
+      <c r="F273" s="10">
+        <v>0</v>
+      </c>
       <c r="G273" s="11" t="s">
         <v>24</v>
       </c>
@@ -6557,7 +6577,9 @@
       <c r="E274" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F274" s="10"/>
+      <c r="F274" s="10">
+        <v>0</v>
+      </c>
       <c r="G274" s="11" t="s">
         <v>24</v>
       </c>
@@ -6588,7 +6610,9 @@
       <c r="E277" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F277" s="10"/>
+      <c r="F277" s="10">
+        <v>0</v>
+      </c>
       <c r="G277" s="10"/>
     </row>
     <row r="278" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -6604,7 +6628,9 @@
       <c r="E278" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F278" s="10"/>
+      <c r="F278" s="10">
+        <v>0</v>
+      </c>
       <c r="G278" s="11" t="s">
         <v>24</v>
       </c>
@@ -6622,7 +6648,9 @@
       <c r="E279" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F279" s="10"/>
+      <c r="F279" s="10">
+        <v>0</v>
+      </c>
       <c r="G279" s="11" t="s">
         <v>24</v>
       </c>
@@ -6653,7 +6681,9 @@
       <c r="E282" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F282" s="10"/>
+      <c r="F282" s="10">
+        <v>0</v>
+      </c>
       <c r="G282" s="10"/>
     </row>
     <row r="283" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -6669,7 +6699,9 @@
       <c r="E283" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F283" s="10"/>
+      <c r="F283" s="10">
+        <v>0</v>
+      </c>
       <c r="G283" s="11" t="s">
         <v>24</v>
       </c>
@@ -6687,7 +6719,9 @@
       <c r="E284" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F284" s="10"/>
+      <c r="F284" s="10">
+        <v>1</v>
+      </c>
       <c r="G284" s="11" t="s">
         <v>24</v>
       </c>
@@ -6718,8 +6752,12 @@
       <c r="E287" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F287" s="10"/>
-      <c r="G287" s="10"/>
+      <c r="F287" s="10">
+        <v>1</v>
+      </c>
+      <c r="G287" s="10" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="288" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B288" s="7" t="s">
@@ -6734,7 +6772,9 @@
       <c r="E288" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F288" s="10"/>
+      <c r="F288" s="10">
+        <v>0</v>
+      </c>
       <c r="G288" s="11" t="s">
         <v>24</v>
       </c>
@@ -6752,7 +6792,9 @@
       <c r="E289" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F289" s="10"/>
+      <c r="F289" s="10">
+        <v>1</v>
+      </c>
       <c r="G289" s="11" t="s">
         <v>24</v>
       </c>
@@ -6770,7 +6812,9 @@
       <c r="E290" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F290" s="10"/>
+      <c r="F290" s="10">
+        <v>0</v>
+      </c>
       <c r="G290" s="11" t="s">
         <v>24</v>
       </c>
@@ -6788,7 +6832,9 @@
       <c r="E291" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F291" s="10"/>
+      <c r="F291" s="10">
+        <v>0</v>
+      </c>
       <c r="G291" s="11" t="s">
         <v>24</v>
       </c>
@@ -6806,7 +6852,9 @@
       <c r="E292" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F292" s="10"/>
+      <c r="F292" s="10">
+        <v>1</v>
+      </c>
       <c r="G292" s="11" t="s">
         <v>24</v>
       </c>
@@ -6837,7 +6885,9 @@
       <c r="E295" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F295" s="10"/>
+      <c r="F295" s="10">
+        <v>0</v>
+      </c>
       <c r="G295" s="11" t="s">
         <v>24</v>
       </c>
@@ -6855,7 +6905,9 @@
       <c r="E296" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F296" s="10"/>
+      <c r="F296" s="10">
+        <v>1</v>
+      </c>
       <c r="G296" s="11" t="s">
         <v>24</v>
       </c>
@@ -6886,7 +6938,9 @@
       <c r="E299" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F299" s="10"/>
+      <c r="F299" s="10">
+        <v>0</v>
+      </c>
       <c r="G299" s="10"/>
     </row>
     <row r="300" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -6902,8 +6956,12 @@
       <c r="E300" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F300" s="10"/>
-      <c r="G300" s="10"/>
+      <c r="F300" s="10">
+        <v>1</v>
+      </c>
+      <c r="G300" s="10" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="301" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B301" s="7" t="s">
@@ -6918,7 +6976,9 @@
       <c r="E301" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F301" s="10"/>
+      <c r="F301" s="10">
+        <v>0</v>
+      </c>
       <c r="G301" s="11" t="s">
         <v>24</v>
       </c>
@@ -6949,7 +7009,9 @@
       <c r="E304" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F304" s="10"/>
+      <c r="F304" s="10">
+        <v>0</v>
+      </c>
       <c r="G304" s="10"/>
     </row>
     <row r="305" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -6965,7 +7027,9 @@
       <c r="E305" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F305" s="10"/>
+      <c r="F305" s="10">
+        <v>0</v>
+      </c>
       <c r="G305" s="10"/>
     </row>
     <row r="306" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -6981,7 +7045,9 @@
       <c r="E306" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F306" s="10"/>
+      <c r="F306" s="10">
+        <v>0</v>
+      </c>
       <c r="G306" s="11" t="s">
         <v>24</v>
       </c>
@@ -6999,7 +7065,9 @@
       <c r="E307" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F307" s="10"/>
+      <c r="F307" s="10">
+        <v>0</v>
+      </c>
       <c r="G307" s="11" t="s">
         <v>24</v>
       </c>
@@ -7017,7 +7085,9 @@
       <c r="E308" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F308" s="10"/>
+      <c r="F308" s="10">
+        <v>0</v>
+      </c>
       <c r="G308" s="11" t="s">
         <v>24</v>
       </c>
@@ -7048,8 +7118,12 @@
       <c r="E311" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F311" s="10"/>
-      <c r="G311" s="10"/>
+      <c r="F311" s="10">
+        <v>1</v>
+      </c>
+      <c r="G311" s="10" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="312" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B312" s="7" t="s">
@@ -7064,7 +7138,9 @@
       <c r="E312" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F312" s="10"/>
+      <c r="F312" s="10">
+        <v>0</v>
+      </c>
       <c r="G312" s="11" t="s">
         <v>24</v>
       </c>
@@ -7082,7 +7158,9 @@
       <c r="E313" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F313" s="10"/>
+      <c r="F313" s="10">
+        <v>1</v>
+      </c>
       <c r="G313" s="11" t="s">
         <v>24</v>
       </c>
@@ -7100,7 +7178,9 @@
       <c r="E314" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F314" s="10"/>
+      <c r="F314" s="10">
+        <v>1</v>
+      </c>
       <c r="G314" s="11" t="s">
         <v>24</v>
       </c>
@@ -7118,7 +7198,9 @@
       <c r="E315" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F315" s="10"/>
+      <c r="F315" s="10">
+        <v>1</v>
+      </c>
       <c r="G315" s="11" t="s">
         <v>24</v>
       </c>
@@ -7136,7 +7218,9 @@
       <c r="E316" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F316" s="10"/>
+      <c r="F316" s="10">
+        <v>0</v>
+      </c>
       <c r="G316" s="11" t="s">
         <v>24</v>
       </c>
@@ -7154,7 +7238,9 @@
       <c r="E317" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F317" s="10"/>
+      <c r="F317" s="10">
+        <v>0</v>
+      </c>
       <c r="G317" s="11" t="s">
         <v>24</v>
       </c>
@@ -7185,7 +7271,9 @@
       <c r="E320" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F320" s="10"/>
+      <c r="F320" s="10">
+        <v>0</v>
+      </c>
       <c r="G320" s="10"/>
     </row>
     <row r="321" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -7201,7 +7289,9 @@
       <c r="E321" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F321" s="10"/>
+      <c r="F321" s="10">
+        <v>0</v>
+      </c>
       <c r="G321" s="11" t="s">
         <v>24</v>
       </c>
@@ -7219,7 +7309,9 @@
       <c r="E322" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F322" s="10"/>
+      <c r="F322" s="10">
+        <v>1</v>
+      </c>
       <c r="G322" s="11" t="s">
         <v>24</v>
       </c>
@@ -7237,7 +7329,9 @@
       <c r="E323" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F323" s="10"/>
+      <c r="F323" s="10">
+        <v>0</v>
+      </c>
       <c r="G323" s="11" t="s">
         <v>24</v>
       </c>
@@ -7255,7 +7349,9 @@
       <c r="E324" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F324" s="10"/>
+      <c r="F324" s="10">
+        <v>0</v>
+      </c>
       <c r="G324" s="11" t="s">
         <v>24</v>
       </c>
@@ -7273,7 +7369,9 @@
       <c r="E325" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F325" s="10"/>
+      <c r="F325" s="10">
+        <v>1</v>
+      </c>
       <c r="G325" s="11" t="s">
         <v>24</v>
       </c>
@@ -7395,7 +7493,9 @@
       <c r="E334" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F334" s="10"/>
+      <c r="F334" s="10">
+        <v>0</v>
+      </c>
       <c r="G334" s="11" t="s">
         <v>24</v>
       </c>
@@ -7413,7 +7513,9 @@
       <c r="E335" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F335" s="10"/>
+      <c r="F335" s="10">
+        <v>1</v>
+      </c>
       <c r="G335" s="11" t="s">
         <v>24</v>
       </c>
@@ -7431,7 +7533,9 @@
       <c r="E336" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F336" s="10"/>
+      <c r="F336" s="10">
+        <v>0</v>
+      </c>
       <c r="G336" s="11" t="s">
         <v>24</v>
       </c>
@@ -7462,7 +7566,9 @@
       <c r="E339" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F339" s="10"/>
+      <c r="F339" s="10">
+        <v>0</v>
+      </c>
       <c r="G339" s="10"/>
     </row>
     <row r="340" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -7478,7 +7584,9 @@
       <c r="E340" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F340" s="10"/>
+      <c r="F340" s="10">
+        <v>0</v>
+      </c>
       <c r="G340" s="11" t="s">
         <v>24</v>
       </c>
@@ -7496,7 +7604,9 @@
       <c r="E341" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F341" s="10"/>
+      <c r="F341" s="10">
+        <v>1</v>
+      </c>
       <c r="G341" s="11" t="s">
         <v>24</v>
       </c>
@@ -7514,7 +7624,9 @@
       <c r="E342" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F342" s="10"/>
+      <c r="F342" s="10">
+        <v>0</v>
+      </c>
       <c r="G342" s="11" t="s">
         <v>24</v>
       </c>
@@ -7532,7 +7644,9 @@
       <c r="E343" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F343" s="10"/>
+      <c r="F343" s="10">
+        <v>0</v>
+      </c>
       <c r="G343" s="11" t="s">
         <v>24</v>
       </c>
@@ -7550,7 +7664,9 @@
       <c r="E344" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F344" s="10"/>
+      <c r="F344" s="10">
+        <v>0</v>
+      </c>
       <c r="G344" s="11" t="s">
         <v>24</v>
       </c>
@@ -7568,7 +7684,9 @@
       <c r="E345" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F345" s="10"/>
+      <c r="F345" s="10">
+        <v>0</v>
+      </c>
       <c r="G345" s="11" t="s">
         <v>24</v>
       </c>
@@ -7599,7 +7717,9 @@
       <c r="E348" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="F348" s="10"/>
+      <c r="F348" s="10">
+        <v>0</v>
+      </c>
       <c r="G348" s="11" t="s">
         <v>24</v>
       </c>
@@ -7617,7 +7737,9 @@
       <c r="E349" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F349" s="10"/>
+      <c r="F349" s="10">
+        <v>0</v>
+      </c>
       <c r="G349" s="11" t="s">
         <v>24</v>
       </c>
@@ -7648,8 +7770,12 @@
       <c r="E352" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F352" s="10"/>
-      <c r="G352" s="10"/>
+      <c r="F352" s="10">
+        <v>1</v>
+      </c>
+      <c r="G352" s="10" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="353" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B353" s="7" t="s">
@@ -7664,7 +7790,9 @@
       <c r="E353" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F353" s="10"/>
+      <c r="F353" s="10">
+        <v>0</v>
+      </c>
       <c r="G353" s="11" t="s">
         <v>24</v>
       </c>
@@ -7682,7 +7810,9 @@
       <c r="E354" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F354" s="10"/>
+      <c r="F354" s="10">
+        <v>1</v>
+      </c>
       <c r="G354" s="11" t="s">
         <v>24</v>
       </c>
@@ -7700,7 +7830,9 @@
       <c r="E355" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F355" s="10"/>
+      <c r="F355" s="10">
+        <v>0</v>
+      </c>
       <c r="G355" s="11" t="s">
         <v>24</v>
       </c>
@@ -7718,7 +7850,9 @@
       <c r="E356" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F356" s="10"/>
+      <c r="F356" s="10">
+        <v>1</v>
+      </c>
       <c r="G356" s="11" t="s">
         <v>24</v>
       </c>
@@ -7880,7 +8014,9 @@
       <c r="E367" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F367" s="10"/>
+      <c r="F367" s="10">
+        <v>0</v>
+      </c>
       <c r="G367" s="11" t="s">
         <v>24</v>
       </c>
@@ -7898,7 +8034,9 @@
       <c r="E368" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F368" s="10"/>
+      <c r="F368" s="10">
+        <v>1</v>
+      </c>
       <c r="G368" s="11" t="s">
         <v>24</v>
       </c>
@@ -7916,7 +8054,9 @@
       <c r="E369" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F369" s="10"/>
+      <c r="F369" s="10">
+        <v>0</v>
+      </c>
       <c r="G369" s="11" t="s">
         <v>24</v>
       </c>
@@ -7947,7 +8087,9 @@
       <c r="E372" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F372" s="10"/>
+      <c r="F372" s="10">
+        <v>0</v>
+      </c>
       <c r="G372" s="11" t="s">
         <v>24</v>
       </c>
@@ -7965,7 +8107,9 @@
       <c r="E373" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F373" s="10"/>
+      <c r="F373" s="10">
+        <v>0</v>
+      </c>
       <c r="G373" s="11" t="s">
         <v>24</v>
       </c>
@@ -7983,7 +8127,9 @@
       <c r="E374" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F374" s="10"/>
+      <c r="F374" s="10">
+        <v>0</v>
+      </c>
       <c r="G374" s="11" t="s">
         <v>24</v>
       </c>
@@ -8014,7 +8160,9 @@
       <c r="E377" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F377" s="10"/>
+      <c r="F377" s="10">
+        <v>0</v>
+      </c>
       <c r="G377" s="10"/>
     </row>
     <row r="378" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -8030,7 +8178,9 @@
       <c r="E378" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F378" s="10"/>
+      <c r="F378" s="10">
+        <v>0</v>
+      </c>
       <c r="G378" s="10"/>
     </row>
     <row r="379" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
@@ -8046,7 +8196,9 @@
       <c r="E379" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F379" s="10"/>
+      <c r="F379" s="10">
+        <v>1</v>
+      </c>
       <c r="G379" s="11" t="s">
         <v>24</v>
       </c>
@@ -10088,8 +10240,12 @@
       <c r="E515" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F515" s="10"/>
-      <c r="G515" s="10"/>
+      <c r="F515" s="10">
+        <v>1</v>
+      </c>
+      <c r="G515" s="10" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="516" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B516" s="7" t="s">
@@ -10104,8 +10260,12 @@
       <c r="E516" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F516" s="10"/>
-      <c r="G516" s="10"/>
+      <c r="F516" s="10">
+        <v>1</v>
+      </c>
+      <c r="G516" s="10" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="517" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B517" s="7" t="s">
@@ -10120,7 +10280,9 @@
       <c r="E517" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F517" s="10"/>
+      <c r="F517" s="10">
+        <v>0</v>
+      </c>
       <c r="G517" s="11" t="s">
         <v>24</v>
       </c>
@@ -10138,7 +10300,9 @@
       <c r="E518" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F518" s="10"/>
+      <c r="F518" s="10">
+        <v>0</v>
+      </c>
       <c r="G518" s="11" t="s">
         <v>24</v>
       </c>
@@ -10156,7 +10320,9 @@
       <c r="E519" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F519" s="10"/>
+      <c r="F519" s="10">
+        <v>0</v>
+      </c>
       <c r="G519" s="11" t="s">
         <v>24</v>
       </c>
